--- a/assets/unit-economics-input.xlsx
+++ b/assets/unit-economics-input.xlsx
@@ -431,8 +431,8 @@
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="4" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
@@ -508,6 +508,17 @@
           <t xml:space="preserve">Value</t>
         </is>
       </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After variable costs</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -519,6 +530,16 @@
         <f>SUMPRODUCT(('Orders'!$E$3:$E$1200*'Orders'!$G$3:$G$1200)-'Orders'!$H$3:$H$1200)</f>
         <v>83755.43</v>
       </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contribution margin</t>
+        </is>
+      </c>
+      <c r="E10" s="6">
+        <f>B11</f>
+        <v>51319.39</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -530,6 +551,16 @@
         <f>SUM(E27:E33)</f>
         <v>51319.39</v>
       </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+ Shipping charged ex VAT</t>
+        </is>
+      </c>
+      <c r="E11" s="6">
+        <f>ROUND(ROUND('Settings'!B13/(1+'Settings'!B6/100),2)*SUMPRODUCT(1/COUNTIF('Orders'!$A$3:$A$1200,'Orders'!$A$3:$A$1200)),2)</f>
+        <v>2174.04</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -541,6 +572,16 @@
         <f>COUNTA('Orders'!$A$3:$A$1200)</f>
         <v>1198</v>
       </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Fulfilment</t>
+        </is>
+      </c>
+      <c r="E12" s="6">
+        <f>ROUND('Settings'!B12*SUMPRODUCT(1/COUNTIF('Orders'!$A$3:$A$1200,'Orders'!$A$3:$A$1200)),2)</f>
+        <v>4811.4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -552,9 +593,30 @@
         <f>SUM('Orders'!$G$3:$G$1200)</f>
         <v>1358</v>
       </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Payment fees</t>
+        </is>
+      </c>
+      <c r="E13" s="6">
+        <f>ROUND('Settings'!B14/100*(B10+'Settings'!B13*SUMPRODUCT(1/COUNTIF('Orders'!$A$3:$A$1200,'Orders'!$A$3:$A$1200)))+'Settings'!B15*SUMPRODUCT(1/COUNTIF('Orders'!$A$3:$A$1200,'Orders'!$A$3:$A$1200)),2)</f>
+        <v>1518.51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Advertising</t>
+        </is>
+      </c>
+      <c r="E14" s="6">
+        <f>SUM('Settings'!$B$19:$B$60)</f>
+        <v>11997</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -566,6 +628,16 @@
         <is>
           <t xml:space="preserve">Value</t>
         </is>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After variable costs</t>
+        </is>
+      </c>
+      <c r="E15" s="11">
+        <f>E10+E11-E12-E13-E14</f>
+        <v>35166.52</v>
       </c>
     </row>
     <row r="16">
@@ -578,6 +650,16 @@
         <f>'Settings'!B8</f>
         <v>100000</v>
       </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Share of net sales</t>
+        </is>
+      </c>
+      <c r="E16" s="7">
+        <f>IF(SUM('Orders'!$I$3:$I$1200)=0,0,E15/SUM('Orders'!$I$3:$I$1200))</f>
+        <v>0.508</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -589,6 +671,13 @@
         <f>B10/B16</f>
         <v>0.8376</v>
       </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costs come from Settings. Not net profit.</t>
+        </is>
+      </c>
+      <c r="E17" s="5"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -939,7 +1028,7 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Live, formula-driven Excel companion. The polished interactive dashboard is online.</t>
+          <t xml:space="preserve">Live, formula-driven Excel companion, including what remains after variable costs. The polished interactive dashboard is online.</t>
         </is>
       </c>
     </row>
